--- a/results/supporting_info/S12_Table_liu_validation.xlsx
+++ b/results/supporting_info/S12_Table_liu_validation.xlsx
@@ -13,12 +13,15 @@
     <sheet name="power" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="marker_values" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="liu9_in_gse267015" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="within_subtype_pattern" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="boundary_tests" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="subtype2_composition" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t xml:space="preserve">tumour</t>
   </si>
@@ -841,6 +844,120 @@
   <si>
     <t xml:space="preserve">RB_8</t>
   </si>
+  <si>
+    <t xml:space="preserve">auc_s1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lo_s1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi_s1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_pos_s1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_s1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auc_s2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lo_s2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi_s2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_pos_s2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_s2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opposite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s1_up_s2_down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fraction of genome altered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copy number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOFA joint factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auc_closeness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_quadratic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_quadratic_adj_subtype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">padj_quadratic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or_unadj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_unadj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proxy vs high risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stroma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endothelial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rpe_melanocyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marker OR per SD, unadjusted vs adjusted for stroma and RPE/melanocyte</t>
+  </si>
 </sst>
 </file>
 
@@ -5614,6 +5731,652 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.495867768595041</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.21493549325458</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.776800043935503</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.479338842975207</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.201033914501382</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.757643771449031</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.89766270880822</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.56198347107438</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.308133626438803</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.815833315709957</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.652184760543894</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.611570247933884</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.359379570387267</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.863760925480501</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.400923122285351</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.429752066115702</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.17078582954369</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.688718302687715</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.606317830776035</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.537190082644628</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.279646190023007</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.79473397526625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.796935778359927</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.526785714285714</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.224026771554779</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.82954465701665</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.867554805016105</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.580357142857143</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.285709893329522</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.875004392384764</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.569890859054946</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.177380918807434</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.697619081192566</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.664233667948838</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.553571428571429</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.272353306785446</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.834789550357411</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.71354410982894</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.455357142857143</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.183546659961163</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.727167625753123</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.763949088407293</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.517857142857143</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.251790179346211</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.783924106368075</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.92033649185352</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" t="s">
+        <v>288</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14" t="n">
+        <v>0.191281895761751</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.146022674281735</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.193470360501757</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.141221313036109</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" t="n">
+        <v>0.240890330663291</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.036387277491141</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.265310307760749</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0650067635463112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" t="n">
+        <v>0.062349817625555</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0476419690709106</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.022088850713163</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0550596281683286</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" t="n">
+        <v>0.247020737231447</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.194530406623169</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.231908743290137</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.184766412190798</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" t="n">
+        <v>0.379386382521854</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.102124888637534</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.381554504320838</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.14394141772377</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" t="n">
+        <v>0.262271205329053</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.151175532341865</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.167377604893751</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.177919071711397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -99932,4 +100695,7980 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K1" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1" t="s">
+        <v>282</v>
+      </c>
+      <c r="M1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.59047619047619</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.287485364043638</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.893467016908743</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.638095238095238</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.426100101215289</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.850090374975187</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.694444444444444</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.231345612828814</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.422619047619048</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.178151887316837</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.667086207921259</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>29</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.605769230769231</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.339376209049849</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.872162252488612</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.429752066115702</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.17302447948611</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.686479652745295</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.722222222222222</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.365946015917237</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.392857142857143</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0994345196433525</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.686279766070933</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.519230769230769</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.233124229305625</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.805337309155914</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.471074380165289</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.212716760736832</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.729431999593747</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.351851851851852</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0411177688324756</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.662585934871228</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.330357142857143</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0722902640362552</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.58842402167803</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.721153846153846</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.49284569267961</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.949461999628082</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.388429752066116</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.136239074519499</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.640620429612733</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.611111111111111</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.229625936909396</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.992596285312826</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.366071428571429</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0787331056318104</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.653409751511047</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.576923076923077</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.309389723144218</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.844456430701936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.347107438016529</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0788841722825248</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.615330703750533</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.907407407407407</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.712545068725776</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0510125146820702</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.663273199603644</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>22</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>288</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.576923076923077</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.312201844556174</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.84164430928998</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.330578512396694</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0779720214142911</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.583185003379097</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>22</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.592592592592593</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2814846565208</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.903700528664385</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.276785714285714</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0253234845029935</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.528247944068435</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>22</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.423076923076923</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.151745909020545</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.694407937133302</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.628099173553719</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.383192379211859</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.873005967895579</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.21230992046528</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.669642857142857</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.41160206017345</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.927683654112264</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>22</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.499171677138711</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.247933884297521</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0248943306976649</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.470973437897376</v>
+      </c>
+      <c r="L16" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" t="n">
+        <v>22</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" t="s">
+        <v>289</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.851851851851852</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.687398555139842</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>21</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.321428571428571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0266328821138265</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.616224260743316</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>288</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.317307692307692</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0696345682900227</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.564980816325362</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>21</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.330578512396694</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0908692706588092</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.570287754134579</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" t="s">
+        <v>289</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.407407407407407</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.172020181100785</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.64279463371403</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.330357142857143</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0370148135547675</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.623699472159518</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>22</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.509615384615385</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.198992871744025</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.820237897486745</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.43801652892562</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.181902879212991</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.694130178638249</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.740740740740741</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.228349648177736</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.473214285714286</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.173606258059728</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.772822313368843</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" t="s">
+        <v>288</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.480769230769231</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.22465305867612</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.736885402862341</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.43801652892562</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.16871938958912</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.70731366826212</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.425925925925926</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.168372842959809</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.683479008892043</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.535714285714286</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.257382996113119</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.814045575315452</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.082709107740587</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.667290892259413</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.487603305785124</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.229347261992371</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.745859349577877</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" t="s">
+        <v>289</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.759259259259259</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.331430655612575</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.464285714285714</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.199817222181666</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.728754206389763</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>22</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>288</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.509615384615385</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.248917750012682</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.770313019218087</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.553719008264463</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.290631567485283</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.816806449043643</v>
+      </c>
+      <c r="L26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.62962962962963</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.317030752416863</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.942228506842397</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>21</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.310556451174542</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.814443548825458</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>22</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.490384615384615</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.21635557528661</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.764413655482621</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>21</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.297520661157025</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0668476971736559</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.528193625140394</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" t="n">
+        <v>22</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.095099788184027</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>21</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.104972338115303</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.609313376170411</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>22</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.471153846153846</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.188990713270001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.753316979037691</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>21</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.196899705525696</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.712191203565213</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>22</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.814814814814815</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.605015513106294</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>21</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.410714285714286</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.150737554717357</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.670691016711214</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>22</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.788461538461538</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.584716696644108</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.992206380278969</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>21</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.40495867768595</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.155592875925708</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.654324479446193</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11</v>
+      </c>
+      <c r="M32" t="n">
+        <v>22</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.656176714802354</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0670242123162864</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.557975787683714</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>22</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" t="s">
+        <v>288</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.644230769230769</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.376349948879882</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.912111589581656</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.355371900826446</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.104642000766945</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.606101800885948</v>
+      </c>
+      <c r="L34" t="n">
+        <v>11</v>
+      </c>
+      <c r="M34" t="n">
+        <v>22</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
+        <v>289</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.777777777777778</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.56871851118549</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.986837044370066</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.383928571428571</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.11573258475343</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.652124558103713</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.519230769230769</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.219427537478386</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.819034000983152</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>21</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.330578512396694</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0969669208488637</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.564190103944525</v>
+      </c>
+      <c r="L36" t="n">
+        <v>11</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.481481481481481</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.984485510016673</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>21</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.383928571428571</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.130227998543627</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.637629144313516</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.538461538461538</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.264370787059947</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.81255228986313</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>21</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.454545454545455</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.196899705525696</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.712191203565213</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.574074074074074</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.145160068420139</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>21</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.464285714285714</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.18921385656707</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.739357572004358</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>22</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.682692307692308</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.433131442779788</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.932253172604827</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>21</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.504132231404959</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.246792172525299</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.761472290284618</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11</v>
+      </c>
+      <c r="M40" t="n">
+        <v>22</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" t="s">
+        <v>289</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.814814814814815</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.573574526405475</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.482142857142857</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.226631483269007</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.737654231016708</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" t="n">
+        <v>22</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.530510769335828</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.969489230664172</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>21</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.256198347107438</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.037794813754458</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.474601880460418</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11</v>
+      </c>
+      <c r="M42" t="n">
+        <v>22</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.925925925925926</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.802684161841709</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>21</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.258928571428571</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.00698502260311334</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.51087212025403</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8</v>
+      </c>
+      <c r="M43" t="n">
+        <v>22</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
+      </c>
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.371856134785202</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.878143865214798</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>21</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.256198347107438</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0377948137544579</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.474601880460418</v>
+      </c>
+      <c r="L44" t="n">
+        <v>11</v>
+      </c>
+      <c r="M44" t="n">
+        <v>22</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>289</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.796296296296296</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.480368526280261</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.348214285714286</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.0860847417616317</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.61034382966694</v>
+      </c>
+      <c r="L45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M45" t="n">
+        <v>22</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>175</v>
+      </c>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.692307692307692</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.443289572884529</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.941325811730855</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>21</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.363636363636364</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.108240838929418</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.619031888343309</v>
+      </c>
+      <c r="L46" t="n">
+        <v>11</v>
+      </c>
+      <c r="M46" t="n">
+        <v>22</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>289</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.925925925925926</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.766497120370775</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>21</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.13705887449775</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.720083982645107</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>22</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.686274509803922</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.473792733662605</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.898756285945238</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>26</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.392857142857143</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.180570120966421</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.605144164747865</v>
+      </c>
+      <c r="L48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M48" t="n">
+        <v>30</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>290</v>
+      </c>
+      <c r="B49" t="s">
+        <v>291</v>
+      </c>
+      <c r="C49" t="s">
+        <v>289</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.863636363636364</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.71117727451397</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" t="n">
+        <v>26</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.386363636363636</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.106362755434122</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.666364517293151</v>
+      </c>
+      <c r="L49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>30</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" t="s">
+        <v>288</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.526785714285714</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.215081774758662</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.838489653812767</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.380952380952381</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.168024620459072</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.59388014144569</v>
+      </c>
+      <c r="L50" t="n">
+        <v>14</v>
+      </c>
+      <c r="M50" t="n">
+        <v>29</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" t="s">
+        <v>289</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.526315789473684</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.106765405791605</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.945866173155764</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>23</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.110663783095908</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.603621931189806</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>29</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.616071428571429</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.353498487240945</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.878644369901912</v>
+      </c>
+      <c r="G52" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>23</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.452380952380952</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.220940541264322</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.683821363497583</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14</v>
+      </c>
+      <c r="M52" t="n">
+        <v>29</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>289</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.56578947368421</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.163227675040682</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.968351272327738</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>23</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.273809523809524</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.0285760504570939</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.519042997161954</v>
+      </c>
+      <c r="L53" t="n">
+        <v>8</v>
+      </c>
+      <c r="M53" t="n">
+        <v>29</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>288</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.159584426005062</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.697558431137795</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" t="n">
+        <v>23</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.452380952380952</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.231904099698614</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.672857805063291</v>
+      </c>
+      <c r="L54" t="n">
+        <v>14</v>
+      </c>
+      <c r="M54" t="n">
+        <v>29</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B55" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>289</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.31578947368421</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.665079979145509</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>23</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.55952380952381</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.335718106985621</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.783329512061998</v>
+      </c>
+      <c r="L55" t="n">
+        <v>8</v>
+      </c>
+      <c r="M55" t="n">
+        <v>29</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" t="s">
+        <v>288</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.340340954826627</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.909659045173374</v>
+      </c>
+      <c r="G56" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" t="n">
+        <v>23</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.209763740043286</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.647379117099571</v>
+      </c>
+      <c r="L56" t="n">
+        <v>14</v>
+      </c>
+      <c r="M56" t="n">
+        <v>29</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" t="s">
+        <v>289</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.513157894736842</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0876611065593096</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.938654682914375</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.44047619047619</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.205722354430664</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.675230026521717</v>
+      </c>
+      <c r="L57" t="n">
+        <v>8</v>
+      </c>
+      <c r="M57" t="n">
+        <v>29</v>
+      </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" t="s">
+        <v>288</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.553571428571429</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.268804822825476</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.838338034317382</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>23</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.533333333333333</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.31449502367089</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.752171642995777</v>
+      </c>
+      <c r="L58" t="n">
+        <v>14</v>
+      </c>
+      <c r="M58" t="n">
+        <v>29</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" t="s">
+        <v>289</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.842105263157895</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.679909971494199</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>23</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.363095238095238</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.151181957526727</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.575008518663749</v>
+      </c>
+      <c r="L59" t="n">
+        <v>8</v>
+      </c>
+      <c r="M59" t="n">
+        <v>29</v>
+      </c>
+      <c r="N59" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" t="s">
+        <v>288</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.508928571428571</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.224879805507926</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.792977337349217</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>23</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.347619047619048</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.141549575362273</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.553688519875822</v>
+      </c>
+      <c r="L60" t="n">
+        <v>14</v>
+      </c>
+      <c r="M60" t="n">
+        <v>29</v>
+      </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.381578947368421</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.808981859797501</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>23</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0589203414060348</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.441079658593965</v>
+      </c>
+      <c r="L61" t="n">
+        <v>8</v>
+      </c>
+      <c r="M61" t="n">
+        <v>29</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" t="s">
+        <v>288</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.215520312821356</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.784479687178644</v>
+      </c>
+      <c r="G62" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.376190476190476</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.164665455762639</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.587715496618313</v>
+      </c>
+      <c r="L62" t="n">
+        <v>14</v>
+      </c>
+      <c r="M62" t="n">
+        <v>29</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.763157894736842</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.511944854564468</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" t="n">
+        <v>23</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.392857142857143</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.117018052656932</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.668696233057354</v>
+      </c>
+      <c r="L63" t="n">
+        <v>8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>29</v>
+      </c>
+      <c r="N63" t="b">
+        <v>1</v>
+      </c>
+      <c r="O63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" t="s">
+        <v>288</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.544642857142857</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.290164397019238</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.799121317266477</v>
+      </c>
+      <c r="G64" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" t="n">
+        <v>23</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.49047619047619</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.267313035717422</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.713639345234959</v>
+      </c>
+      <c r="L64" t="n">
+        <v>14</v>
+      </c>
+      <c r="M64" t="n">
+        <v>29</v>
+      </c>
+      <c r="N64" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" t="s">
+        <v>289</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.736842105263158</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.498458483393645</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.97522572713267</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" t="n">
+        <v>23</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.249269801484673</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.667396865181994</v>
+      </c>
+      <c r="L65" t="n">
+        <v>8</v>
+      </c>
+      <c r="M65" t="n">
+        <v>29</v>
+      </c>
+      <c r="N65" t="b">
+        <v>1</v>
+      </c>
+      <c r="O65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>288</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.366071428571429</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.133911959309668</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.598230897833189</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>23</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.614285714285714</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.401893599315278</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.82667782925615</v>
+      </c>
+      <c r="L66" t="n">
+        <v>14</v>
+      </c>
+      <c r="M66" t="n">
+        <v>29</v>
+      </c>
+      <c r="N66" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.289473684210526</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0605786549090869</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.518368713511966</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" t="n">
+        <v>23</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.595238095238095</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.383379873765625</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.807096316710565</v>
+      </c>
+      <c r="L67" t="n">
+        <v>8</v>
+      </c>
+      <c r="M67" t="n">
+        <v>29</v>
+      </c>
+      <c r="N67" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" t="s">
+        <v>288</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.491071428571429</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.215338092732425</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.766804764410432</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>23</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.685714285714286</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.48495532629273</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.886473245135841</v>
+      </c>
+      <c r="L68" t="n">
+        <v>14</v>
+      </c>
+      <c r="M68" t="n">
+        <v>29</v>
+      </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" t="s">
+        <v>289</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.578947368421053</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.191730500701238</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.966164236140868</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>23</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.595238095238095</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.313916546750855</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.876559643725335</v>
+      </c>
+      <c r="L69" t="n">
+        <v>8</v>
+      </c>
+      <c r="M69" t="n">
+        <v>29</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.571428571428571</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.241616500211226</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.901240642645917</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" t="n">
+        <v>23</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.414285714285714</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.193022258247449</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.635549170323979</v>
+      </c>
+      <c r="L70" t="n">
+        <v>14</v>
+      </c>
+      <c r="M70" t="n">
+        <v>29</v>
+      </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.921052631578947</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.796776883209011</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" t="n">
+        <v>23</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.055301526117357</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.444698473882643</v>
+      </c>
+      <c r="L71" t="n">
+        <v>8</v>
+      </c>
+      <c r="M71" t="n">
+        <v>29</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" t="s">
+        <v>288</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.678571428571429</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.457446758618503</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.899696098524354</v>
+      </c>
+      <c r="G72" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" t="n">
+        <v>23</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.433333333333333</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.205801323948905</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.660865342717762</v>
+      </c>
+      <c r="L72" t="n">
+        <v>14</v>
+      </c>
+      <c r="M72" t="n">
+        <v>29</v>
+      </c>
+      <c r="N72" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" t="s">
+        <v>289</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.776315789473684</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.552811124569994</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.999820454377374</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4</v>
+      </c>
+      <c r="H73" t="n">
+        <v>23</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.428571428571429</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.131029514226655</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.726113342916202</v>
+      </c>
+      <c r="L73" t="n">
+        <v>8</v>
+      </c>
+      <c r="M73" t="n">
+        <v>29</v>
+      </c>
+      <c r="N73" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" t="s">
+        <v>288</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.651785714285714</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.399847063148686</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.903724365422743</v>
+      </c>
+      <c r="G74" t="n">
+        <v>7</v>
+      </c>
+      <c r="H74" t="n">
+        <v>23</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.380952380952381</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.161491641268613</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.600413120636148</v>
+      </c>
+      <c r="L74" t="n">
+        <v>14</v>
+      </c>
+      <c r="M74" t="n">
+        <v>29</v>
+      </c>
+      <c r="N74" t="b">
+        <v>1</v>
+      </c>
+      <c r="O74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>205</v>
+      </c>
+      <c r="B75" t="s">
+        <v>183</v>
+      </c>
+      <c r="C75" t="s">
+        <v>289</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.407894736842105</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.145741805484933</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.670047668199278</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="n">
+        <v>23</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.255952380952381</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.0257483720179585</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.486156389886803</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>29</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.111650673351969</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.638349326648031</v>
+      </c>
+      <c r="G76" t="n">
+        <v>7</v>
+      </c>
+      <c r="H76" t="n">
+        <v>23</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.595238095238095</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.377094188753408</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.813382001722783</v>
+      </c>
+      <c r="L76" t="n">
+        <v>14</v>
+      </c>
+      <c r="M76" t="n">
+        <v>29</v>
+      </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" t="s">
+        <v>289</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.36886285117025</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.894295043566592</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>23</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.245246626083441</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.754753373916559</v>
+      </c>
+      <c r="L77" t="n">
+        <v>8</v>
+      </c>
+      <c r="M77" t="n">
+        <v>29</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" t="s">
+        <v>288</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.651785714285714</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.400333744835229</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9032376837362</v>
+      </c>
+      <c r="G78" t="n">
+        <v>7</v>
+      </c>
+      <c r="H78" t="n">
+        <v>23</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.181553526817859</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.618446473182141</v>
+      </c>
+      <c r="L78" t="n">
+        <v>14</v>
+      </c>
+      <c r="M78" t="n">
+        <v>29</v>
+      </c>
+      <c r="N78" t="b">
+        <v>1</v>
+      </c>
+      <c r="O78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" t="s">
+        <v>289</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.81578947368421</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.555759273063247</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>23</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.0198147681057708</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.396851898560896</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8</v>
+      </c>
+      <c r="M79" t="n">
+        <v>29</v>
+      </c>
+      <c r="N79" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>202</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" t="s">
+        <v>288</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.633928571428571</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.358269287782616</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.909587855074527</v>
+      </c>
+      <c r="G80" t="n">
+        <v>7</v>
+      </c>
+      <c r="H80" t="n">
+        <v>23</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.352380952380952</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.140394846370116</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.564367058391789</v>
+      </c>
+      <c r="L80" t="n">
+        <v>14</v>
+      </c>
+      <c r="M80" t="n">
+        <v>29</v>
+      </c>
+      <c r="N80" t="b">
+        <v>1</v>
+      </c>
+      <c r="O80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.894736842105263</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.742895322648484</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>23</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.19047619047619</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.0217528521797239</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.359199528772657</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8</v>
+      </c>
+      <c r="M81" t="n">
+        <v>29</v>
+      </c>
+      <c r="N81" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" t="s">
+        <v>288</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.642857142857143</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.356090144993452</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.929624140720833</v>
+      </c>
+      <c r="G82" t="n">
+        <v>7</v>
+      </c>
+      <c r="H82" t="n">
+        <v>23</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.485714285714286</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.257787160315148</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.713641411113423</v>
+      </c>
+      <c r="L82" t="n">
+        <v>14</v>
+      </c>
+      <c r="M82" t="n">
+        <v>29</v>
+      </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>289</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.776315789473684</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.368284150426131</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" t="n">
+        <v>23</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.126525302254222</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.623474697745778</v>
+      </c>
+      <c r="L83" t="n">
+        <v>8</v>
+      </c>
+      <c r="M83" t="n">
+        <v>29</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" t="s">
+        <v>288</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.473214285714286</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.21009763411682</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.736330937311752</v>
+      </c>
+      <c r="G84" t="n">
+        <v>7</v>
+      </c>
+      <c r="H84" t="n">
+        <v>23</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.40952380952381</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.185288741435677</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.633758877611942</v>
+      </c>
+      <c r="L84" t="n">
+        <v>14</v>
+      </c>
+      <c r="M84" t="n">
+        <v>29</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.421052631578947</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.195081860420616</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.647023402737279</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" t="n">
+        <v>23</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.488095238095238</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.224109874512271</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.752080601678205</v>
+      </c>
+      <c r="L85" t="n">
+        <v>8</v>
+      </c>
+      <c r="M85" t="n">
+        <v>29</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" t="s">
+        <v>288</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.491071428571429</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.236753472065242</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.745389385077615</v>
+      </c>
+      <c r="G86" t="n">
+        <v>7</v>
+      </c>
+      <c r="H86" t="n">
+        <v>23</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.480952380952381</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.258784434896175</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.703120327008587</v>
+      </c>
+      <c r="L86" t="n">
+        <v>14</v>
+      </c>
+      <c r="M86" t="n">
+        <v>29</v>
+      </c>
+      <c r="N86" t="b">
+        <v>0</v>
+      </c>
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s">
+        <v>183</v>
+      </c>
+      <c r="C87" t="s">
+        <v>289</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.412583244894179</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.850574649842664</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>23</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.648809523809524</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.393564336514943</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.904054711104104</v>
+      </c>
+      <c r="L87" t="n">
+        <v>8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>29</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" t="s">
+        <v>288</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.741071428571429</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.474294584746383</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>7</v>
+      </c>
+      <c r="H88" t="n">
+        <v>23</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.380952380952381</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.16061667655302</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.601288085351741</v>
+      </c>
+      <c r="L88" t="n">
+        <v>14</v>
+      </c>
+      <c r="M88" t="n">
+        <v>29</v>
+      </c>
+      <c r="N88" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>192</v>
+      </c>
+      <c r="B89" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" t="s">
+        <v>289</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.604162441412685</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>23</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.273809523809524</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.0378536464150971</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.509765401203951</v>
+      </c>
+      <c r="L89" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" t="n">
+        <v>29</v>
+      </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" t="s">
+        <v>183</v>
+      </c>
+      <c r="C90" t="s">
+        <v>288</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.589285714285714</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.294514379193764</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.884057049377665</v>
+      </c>
+      <c r="G90" t="n">
+        <v>7</v>
+      </c>
+      <c r="H90" t="n">
+        <v>23</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.538095238095238</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.31832503335635</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.757865442834126</v>
+      </c>
+      <c r="L90" t="n">
+        <v>14</v>
+      </c>
+      <c r="M90" t="n">
+        <v>29</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.31578947368421</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00871863071648444</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.622860316651937</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>23</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.672619047619048</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.45888767666551</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.886350418572585</v>
+      </c>
+      <c r="L91" t="n">
+        <v>8</v>
+      </c>
+      <c r="M91" t="n">
+        <v>29</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" t="s">
+        <v>288</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.589285714285714</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.299508793269513</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.879062635301915</v>
+      </c>
+      <c r="G92" t="n">
+        <v>7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>23</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.29047619047619</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.0911359724320681</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.489816408520313</v>
+      </c>
+      <c r="L92" t="n">
+        <v>14</v>
+      </c>
+      <c r="M92" t="n">
+        <v>29</v>
+      </c>
+      <c r="N92" t="b">
+        <v>1</v>
+      </c>
+      <c r="O92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" t="s">
+        <v>289</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.679497193019842</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>23</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.136904761904762</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.274563249184491</v>
+      </c>
+      <c r="L93" t="n">
+        <v>8</v>
+      </c>
+      <c r="M93" t="n">
+        <v>29</v>
+      </c>
+      <c r="N93" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" t="s">
+        <v>183</v>
+      </c>
+      <c r="C94" t="s">
+        <v>288</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.589285714285714</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.297857829514629</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.8807135990568</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7</v>
+      </c>
+      <c r="H94" t="n">
+        <v>23</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.371428571428571</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.160472249900142</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.582384892957001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>14</v>
+      </c>
+      <c r="M94" t="n">
+        <v>29</v>
+      </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" t="s">
+        <v>183</v>
+      </c>
+      <c r="C95" t="s">
+        <v>289</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.174758441690005</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>23</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.386904761904762</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.141259344192512</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.632550179617012</v>
+      </c>
+      <c r="L95" t="n">
+        <v>8</v>
+      </c>
+      <c r="M95" t="n">
+        <v>29</v>
+      </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" t="s">
+        <v>288</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.464285714285714</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.196897346807104</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.731674081764325</v>
+      </c>
+      <c r="G96" t="n">
+        <v>7</v>
+      </c>
+      <c r="H96" t="n">
+        <v>23</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.277888072628653</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.722111927371347</v>
+      </c>
+      <c r="L96" t="n">
+        <v>14</v>
+      </c>
+      <c r="M96" t="n">
+        <v>29</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" t="s">
+        <v>289</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.368421052631579</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.0522208511562577</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.6846212541069</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>23</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.642857142857143</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.421220866235643</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.864493419478643</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>29</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" t="s">
+        <v>296</v>
+      </c>
+      <c r="K1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.378571428571429</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.220491047064676</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.536651810078181</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.589140931991675</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.555824263090445</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.511752136752137</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.320700062168489</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.702804211335784</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.484381906196591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.528565151706426</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.537280701754386</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.357509991403316</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.717051412105456</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.420377961695556</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.438321490478008</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.568181818181818</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.346769648170623</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.789593988193013</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.550540759463178</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.706889979037957</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.695419906690331</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.552631578947368</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.370705780529968</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.734557377364769</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.31384706697824</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.384693010361281</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" t="n">
+        <v>43</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.605113636363636</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.398172950741517</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.812054321985756</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.289357970172911</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.663167689088308</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.600877192982456</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.423301793195795</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.778452592769117</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.485285205911125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.942401819972742</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.571022727272727</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.360936088318122</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.781109366227333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.764296616337812</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.287462024509352</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.853168315911976</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.607456140350877</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.42624380472614</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.788668475975614</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.815377537099846</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.998541892937622</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.755681818181818</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.524113966901642</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.987249669461995</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.253700083625032</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.293405563204411</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>288</v>
+      </c>
+      <c r="D12" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.611842105263158</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.434664447862225</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.789019762664091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.355476440257596</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.827202607227504</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" t="n">
+        <v>43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.627840909090909</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.423938221304059</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.83174359687776</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.183106814912814</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.823264014657297</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.511483245121883</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D14" t="n">
+        <v>43</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.462719298245614</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.281272191033732</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.644166405457496</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.593284173892578</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.660853145424186</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.377840909090909</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.196001576876529</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.559680241305289</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.510779915610439</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.642792167829413</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" t="n">
+        <v>43</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.721491228070175</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.552547241761096</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.890435214379255</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0872000236645422</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.391244597497593</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" t="s">
+        <v>289</v>
+      </c>
+      <c r="D17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.605113636363636</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.38053066928901</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.829696603438262</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.658118506682948</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.332244287012674</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.770480202945891</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>288</v>
+      </c>
+      <c r="D18" t="n">
+        <v>43</v>
+      </c>
+      <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.280139067885739</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.636527598780928</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.591423571062916</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.224256978062274</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" t="s">
+        <v>289</v>
+      </c>
+      <c r="D19" t="n">
+        <v>43</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.477272727272727</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.273232749753256</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.681312704792199</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.652163472658217</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.15296248645016</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.770480202945891</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" t="n">
+        <v>43</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.49780701754386</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.316327204243405</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.679286830844314</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.825314217533386</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.72292871983758</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D21" t="n">
+        <v>43</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.477272727272727</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.260386295010304</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.694159159535151</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.966550629481648</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.878485699433419</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.990505065367789</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" t="s">
+        <v>288</v>
+      </c>
+      <c r="D22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.539473684210526</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.357667624518867</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.721279743902186</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.292464635101871</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.227617483810579</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.738858025520517</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" t="n">
+        <v>43</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.485795454545455</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.279650335353179</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.69194057373773</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.495711121331725</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.289306662385833</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" t="n">
+        <v>43</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.43640350877193</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.256594079338794</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.616212938205066</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.614001709498545</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.580684851865462</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" t="s">
+        <v>289</v>
+      </c>
+      <c r="D25" t="n">
+        <v>43</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.579545454545455</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.369076421026257</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.790014488064652</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.158859241848624</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.16690289385783</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.508349573915596</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>288</v>
+      </c>
+      <c r="D26" t="n">
+        <v>43</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.451236698080595</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.798763301919405</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.410959005534936</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.424905178310104</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" t="n">
+        <v>43</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.644886363636364</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.458179251275407</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.83159347599732</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.117557470405503</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.134528319874016</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" t="n">
+        <v>43</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.592105263157895</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.417864697483527</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.766345828832262</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.28125088862993</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.187402302459263</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.738858025520517</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" t="n">
+        <v>43</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.582386363636364</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.37425682892111</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.790515898351618</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.502025560950821</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.51878852826257</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" t="n">
+        <v>43</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.535087719298246</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.347352375859621</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.72282306273687</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.821799858101499</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.731881197912733</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" t="n">
+        <v>43</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.732954545454545</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.531819816517434</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.934089274391657</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.0914999923541261</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.120866694848022</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" t="n">
+        <v>43</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.642543859649123</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.471374415187174</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.813713304111072</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.137806860405965</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.146788196109479</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" t="n">
+        <v>43</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.670454545454545</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.473504829514742</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.867404261394349</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.120936037426468</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.233102779329294</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" t="s">
+        <v>288</v>
+      </c>
+      <c r="D34" t="n">
+        <v>43</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.638157894736842</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.459560904998032</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.816754884475652</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.28141612603012</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.418726869289801</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.738858025520517</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
+        <v>289</v>
+      </c>
+      <c r="D35" t="n">
+        <v>43</v>
+      </c>
+      <c r="E35" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.613636363636364</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.40074970382919</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.826523023443537</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.111605166934158</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.213780843320836</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" t="n">
+        <v>43</v>
+      </c>
+      <c r="E36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.592105263157895</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.413972361659355</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.770238164656434</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.262366429948274</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.632051988254875</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.738858025520517</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" t="n">
+        <v>43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.559659090909091</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.34668506870202</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.772633113116162</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.291445211392386</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.955787572004266</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D38" t="n">
+        <v>43</v>
+      </c>
+      <c r="E38" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.578947368421053</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.399446682497202</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.758448054344904</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.39067104053397</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.416297051005654</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" t="n">
+        <v>43</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.385809878089187</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.801690121910813</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.317696133248656</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.439035953154631</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.586515938305211</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D40" t="n">
+        <v>43</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.570175438596491</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.388443764575713</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.751907112617269</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.184015742505767</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.175025243974705</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.697316173027116</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" t="s">
+        <v>289</v>
+      </c>
+      <c r="D41" t="n">
+        <v>43</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.565340909090909</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.339522016813062</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.791159801368756</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0834259627949616</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.109770173834646</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" t="n">
+        <v>43</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.706140350877193</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.54566155933184</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.866619142422546</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.0676568962522417</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0893805639309875</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" t="n">
+        <v>43</v>
+      </c>
+      <c r="E43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.529100135331754</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.908399864668246</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0590096973660487</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.0911683268775108</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D44" t="n">
+        <v>43</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.679824561403509</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.517688432112972</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.841960690694045</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0436786373388392</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0387241839655661</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>289</v>
+      </c>
+      <c r="D45" t="n">
+        <v>43</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.661931818181818</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.474465079855127</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.84939855650851</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.088763766729333</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.099443727730277</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>175</v>
+      </c>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" t="n">
+        <v>43</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.618421052631579</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.436181804097065</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.800660301166093</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.622954711826291</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.622692713946381</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>175</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>289</v>
+      </c>
+      <c r="D47" t="n">
+        <v>43</v>
+      </c>
+      <c r="E47" t="n">
+        <v>11</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.707386363636364</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.479932069289848</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.934840657982879</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.289634023670301</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.244793435194349</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>288</v>
+      </c>
+      <c r="D48" t="n">
+        <v>56</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.640316205533597</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.487645761801202</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.792986649265991</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0957060398331316</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.118145689814169</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>290</v>
+      </c>
+      <c r="B49" t="s">
+        <v>291</v>
+      </c>
+      <c r="C49" t="s">
+        <v>289</v>
+      </c>
+      <c r="D49" t="n">
+        <v>56</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.689393939393939</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.487592846177208</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.891195032610671</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.119843498763869</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.106713044287877</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" t="s">
+        <v>288</v>
+      </c>
+      <c r="D50" t="n">
+        <v>52</v>
+      </c>
+      <c r="E50" t="n">
+        <v>21</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.360983102918587</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.207540880329604</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.51442532550757</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.127933242661788</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.126739473718097</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" t="s">
+        <v>289</v>
+      </c>
+      <c r="D51" t="n">
+        <v>52</v>
+      </c>
+      <c r="E51" t="n">
+        <v>12</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.20488383782296</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.586782828843706</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.149320281664354</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.150614319312865</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.508349573915596</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52" t="n">
+        <v>52</v>
+      </c>
+      <c r="E52" t="n">
+        <v>21</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.491551459293395</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.329846831888593</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.653256086698197</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.961129106078133</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.7080049162334</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.961158345756955</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>289</v>
+      </c>
+      <c r="D53" t="n">
+        <v>52</v>
+      </c>
+      <c r="E53" t="n">
+        <v>12</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.314727429748629</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.722772570251371</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.688368181437883</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.346126496813391</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.786706493071867</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>288</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" t="n">
+        <v>21</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.572964669738863</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.405801815627215</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.740127523850512</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.864016574883283</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.914734144776438</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B55" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>289</v>
+      </c>
+      <c r="D55" t="n">
+        <v>52</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.388147007104733</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.811852992895267</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.474065830721837</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.483735703226741</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" t="s">
+        <v>288</v>
+      </c>
+      <c r="D56" t="n">
+        <v>52</v>
+      </c>
+      <c r="E56" t="n">
+        <v>21</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.551459293394777</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.381956764372097</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.720961822417457</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.723268651988968</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.976367305285792</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.890176802447961</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" t="s">
+        <v>289</v>
+      </c>
+      <c r="D57" t="n">
+        <v>52</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.399172450811763</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.829994215854903</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.286224695746073</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.381312044399043</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" t="s">
+        <v>288</v>
+      </c>
+      <c r="D58" t="n">
+        <v>52</v>
+      </c>
+      <c r="E58" t="n">
+        <v>21</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.43778801843318</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.276836276221325</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.598739760645035</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.961158345756955</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.799727911010951</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.961158345756955</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" t="s">
+        <v>289</v>
+      </c>
+      <c r="D59" t="n">
+        <v>52</v>
+      </c>
+      <c r="E59" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.58125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.407055147840132</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.755444852159868</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.203053015950267</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.147788680399003</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.512976040295412</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" t="s">
+        <v>288</v>
+      </c>
+      <c r="D60" t="n">
+        <v>52</v>
+      </c>
+      <c r="E60" t="n">
+        <v>21</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.486943164362519</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.324754388886833</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.649131939838205</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.577142907524796</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6721124073346</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" t="n">
+        <v>52</v>
+      </c>
+      <c r="E61" t="n">
+        <v>12</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.460416666666667</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.270642945904313</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.65019038742902</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.262678706271332</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.287396631222045</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.559574805873381</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" t="s">
+        <v>288</v>
+      </c>
+      <c r="D62" t="n">
+        <v>52</v>
+      </c>
+      <c r="E62" t="n">
+        <v>21</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.592933947772657</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.429585927104198</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.756281968441117</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.156449293416356</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.594961964617781</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" t="n">
+        <v>52</v>
+      </c>
+      <c r="E63" t="n">
+        <v>12</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.448054658918856</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.851945341081144</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.191806216920706</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.295869161164408</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.511483245121883</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" t="s">
+        <v>288</v>
+      </c>
+      <c r="D64" t="n">
+        <v>52</v>
+      </c>
+      <c r="E64" t="n">
+        <v>21</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.640552995391705</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.480012892734653</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.801093098048757</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.337296700994838</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.197914598383275</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" t="s">
+        <v>289</v>
+      </c>
+      <c r="D65" t="n">
+        <v>52</v>
+      </c>
+      <c r="E65" t="n">
+        <v>12</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.6625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.49938015325222</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.82561984674778</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.176507543814575</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.137904378631833</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.511483245121883</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>288</v>
+      </c>
+      <c r="D66" t="n">
+        <v>52</v>
+      </c>
+      <c r="E66" t="n">
+        <v>21</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.490015360983103</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.328043760063895</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.65198696190231</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.749292280006539</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.770107223615895</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.899150736007847</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" t="n">
+        <v>52</v>
+      </c>
+      <c r="E67" t="n">
+        <v>12</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.539583333333333</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.346262125626041</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.732904541040625</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.582305284038567</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.595448739844841</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.716683426509005</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" t="s">
+        <v>288</v>
+      </c>
+      <c r="D68" t="n">
+        <v>52</v>
+      </c>
+      <c r="E68" t="n">
+        <v>21</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.391705069124424</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.227903578867369</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.555506559381479</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.385886719990919</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.384497215157942</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" t="s">
+        <v>289</v>
+      </c>
+      <c r="D69" t="n">
+        <v>52</v>
+      </c>
+      <c r="E69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.433333333333333</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.225268362362674</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.641398304303993</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.468308870427998</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.461941140445801</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" t="n">
+        <v>52</v>
+      </c>
+      <c r="E70" t="n">
+        <v>21</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.45468509984639</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.283426076149871</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.62594412354291</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.203383883799576</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.26051825234152</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.697316173027116</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" t="n">
+        <v>52</v>
+      </c>
+      <c r="E71" t="n">
+        <v>12</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.591666666666667</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.401452940944517</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.781880392388816</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.877646556782888</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.79686672787405</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.957432607399514</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" t="s">
+        <v>288</v>
+      </c>
+      <c r="D72" t="n">
+        <v>52</v>
+      </c>
+      <c r="E72" t="n">
+        <v>21</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.634408602150538</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.480560297477539</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.788256906823537</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.128292615180719</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.131278443122026</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" t="s">
+        <v>289</v>
+      </c>
+      <c r="D73" t="n">
+        <v>52</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.485747379969489</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.864252620030511</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.0734339543981631</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.073060160166052</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" t="s">
+        <v>288</v>
+      </c>
+      <c r="D74" t="n">
+        <v>52</v>
+      </c>
+      <c r="E74" t="n">
+        <v>21</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.334869431643625</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.179007554983509</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.490731308303741</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.0518996687695915</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.0851921990129482</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>205</v>
+      </c>
+      <c r="B75" t="s">
+        <v>183</v>
+      </c>
+      <c r="C75" t="s">
+        <v>289</v>
+      </c>
+      <c r="D75" t="n">
+        <v>52</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.241889296203787</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.653944037129547</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.472536689442189</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.463595130135611</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" t="n">
+        <v>52</v>
+      </c>
+      <c r="E76" t="n">
+        <v>21</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.427035330261137</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.265327900147403</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.58874276037487</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.195261026392161</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.24782224283462</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.697316173027116</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" t="s">
+        <v>289</v>
+      </c>
+      <c r="D77" t="n">
+        <v>52</v>
+      </c>
+      <c r="E77" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.29070057275203</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.65929942724797</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.901731272434444</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.783817190481845</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.961846690596741</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" t="s">
+        <v>288</v>
+      </c>
+      <c r="D78" t="n">
+        <v>52</v>
+      </c>
+      <c r="E78" t="n">
+        <v>21</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.566820276497696</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.404846810180197</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.728793742815195</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.356137093962262</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.425426464304224</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" t="s">
+        <v>289</v>
+      </c>
+      <c r="D79" t="n">
+        <v>52</v>
+      </c>
+      <c r="E79" t="n">
+        <v>12</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.710416666666667</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.558424480698437</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.862408852634897</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.04036705079056</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.0493830521672136</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>202</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" t="s">
+        <v>288</v>
+      </c>
+      <c r="D80" t="n">
+        <v>52</v>
+      </c>
+      <c r="E80" t="n">
+        <v>21</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.516129032258065</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.352267604447505</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.679990460068624</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.569727100666852</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.50236179828478</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" t="n">
+        <v>52</v>
+      </c>
+      <c r="E81" t="n">
+        <v>12</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.720833333333333</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.56075632201148</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.880910344655186</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.0720237552690312</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.070485084965666</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" t="s">
+        <v>288</v>
+      </c>
+      <c r="D82" t="n">
+        <v>52</v>
+      </c>
+      <c r="E82" t="n">
+        <v>21</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.436251920122888</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.278851656020615</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.593652184225161</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.150115861960906</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.196065831489147</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>289</v>
+      </c>
+      <c r="D83" t="n">
+        <v>52</v>
+      </c>
+      <c r="E83" t="n">
+        <v>12</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.508333333333333</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.332345197581166</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.6843214690855</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.133744978438682</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.160230328831266</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.493827612696673</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" t="s">
+        <v>288</v>
+      </c>
+      <c r="D84" t="n">
+        <v>52</v>
+      </c>
+      <c r="E84" t="n">
+        <v>21</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.459293394777266</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.298933127899097</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.619653661655434</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.839948095397719</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.774733465833601</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" t="n">
+        <v>52</v>
+      </c>
+      <c r="E85" t="n">
+        <v>12</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.268337902496959</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.627495430836375</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.969869543172627</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.947140942925746</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.990505065367789</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" t="s">
+        <v>288</v>
+      </c>
+      <c r="D86" t="n">
+        <v>52</v>
+      </c>
+      <c r="E86" t="n">
+        <v>21</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.505376344086022</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.340021711091463</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.67073097708058</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.633750180314174</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.914058310000217</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s">
+        <v>183</v>
+      </c>
+      <c r="C87" t="s">
+        <v>289</v>
+      </c>
+      <c r="D87" t="n">
+        <v>52</v>
+      </c>
+      <c r="E87" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.22507047359422</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.61242952640578</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.999397580243687</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.872483942073955</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.999397580243687</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" t="s">
+        <v>288</v>
+      </c>
+      <c r="D88" t="n">
+        <v>52</v>
+      </c>
+      <c r="E88" t="n">
+        <v>21</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.365591397849462</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.209221484432865</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.52196131126606</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.28967002123415</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.449792878244471</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.738858025520517</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>192</v>
+      </c>
+      <c r="B89" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" t="s">
+        <v>289</v>
+      </c>
+      <c r="D89" t="n">
+        <v>52</v>
+      </c>
+      <c r="E89" t="n">
+        <v>12</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.402083333333333</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.211764002590864</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.592402664075802</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.384606020777257</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.521533295675284</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.659324607046727</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" t="s">
+        <v>183</v>
+      </c>
+      <c r="C90" t="s">
+        <v>288</v>
+      </c>
+      <c r="D90" t="n">
+        <v>52</v>
+      </c>
+      <c r="E90" t="n">
+        <v>21</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.548387096774194</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.382266793938547</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.71450739960984</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.567355917297152</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.453953955959823</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.800526543554746</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" t="n">
+        <v>52</v>
+      </c>
+      <c r="E91" t="n">
+        <v>12</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.454166666666667</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.230929975105266</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.677403358228067</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.406935301932506</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.458791243106337</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" t="s">
+        <v>288</v>
+      </c>
+      <c r="D92" t="n">
+        <v>52</v>
+      </c>
+      <c r="E92" t="n">
+        <v>21</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.568356374807988</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.403696641121804</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.733016108494172</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.431725702803915</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.473266938194064</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.740101204806711</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" t="s">
+        <v>289</v>
+      </c>
+      <c r="D93" t="n">
+        <v>52</v>
+      </c>
+      <c r="E93" t="n">
+        <v>12</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.754166666666667</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.603162916839708</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.905170416493626</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.0460422044108192</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.0468061888286222</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.483744149705872</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" t="s">
+        <v>183</v>
+      </c>
+      <c r="C94" t="s">
+        <v>288</v>
+      </c>
+      <c r="D94" t="n">
+        <v>52</v>
+      </c>
+      <c r="E94" t="n">
+        <v>21</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.61136712749616</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.447762201866736</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.774972053125583</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.112851156948582</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.263835097027043</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.682687825816828</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" t="s">
+        <v>183</v>
+      </c>
+      <c r="C95" t="s">
+        <v>289</v>
+      </c>
+      <c r="D95" t="n">
+        <v>52</v>
+      </c>
+      <c r="E95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.629166666666667</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.415362659213744</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.842970674119589</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.334517162886966</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.554151369056891</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.594697178465717</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" t="s">
+        <v>288</v>
+      </c>
+      <c r="D96" t="n">
+        <v>52</v>
+      </c>
+      <c r="E96" t="n">
+        <v>21</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.571428571428572</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.402828622956517</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.740028519900626</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.861413912653369</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.774933116342247</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.901582512921686</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" t="s">
+        <v>289</v>
+      </c>
+      <c r="D97" t="n">
+        <v>52</v>
+      </c>
+      <c r="E97" t="n">
+        <v>12</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.239295941604698</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.635704058395302</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.441720912259711</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.468602490726532</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.662633404035164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>